--- a/EVAL_Results.xlsx
+++ b/EVAL_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C9972E-1E9C-4FDF-BFED-542D159C09D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BB7434-60B7-45C6-9173-BE34E8C1FCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{445614D9-AB8F-4E7E-91D1-E797337732AC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{445614D9-AB8F-4E7E-91D1-E797337732AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="55">
   <si>
     <t>Life Cycle Cost</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Variables</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -280,10 +283,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -302,6 +301,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,22 +640,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20D1EEE-7447-4E99-A041-A03D80BC56FB}">
   <dimension ref="B1:L34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" customWidth="1"/>
-    <col min="9" max="9" width="23.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.5546875" customWidth="1"/>
     <col min="10" max="10" width="33" customWidth="1"/>
     <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="26.7109375" customWidth="1"/>
+    <col min="12" max="12" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -660,10 +663,10 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>2143.9</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+        <v>2137.9299999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -671,9 +674,8 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>86.204999999999998</v>
-      </c>
-      <c r="G3" s="4"/>
+        <v>86.002499999999998</v>
+      </c>
       <c r="H3" s="2" t="s">
         <v>0</v>
       </c>
@@ -690,7 +692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -698,9 +700,8 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>535975</v>
-      </c>
-      <c r="G4" s="4"/>
+        <v>482292.5</v>
+      </c>
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
@@ -717,7 +718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -725,29 +726,29 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>535975</v>
+        <v>52190</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="5" cm="1">
+      <c r="H5" s="3" cm="1">
         <f t="array" ref="H5:L5">TRANSPOSE(D2:D6)</f>
-        <v>2143.9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>86.204999999999998</v>
-      </c>
-      <c r="J5" s="5">
-        <v>535975</v>
-      </c>
-      <c r="K5" s="5">
-        <v>535975</v>
-      </c>
-      <c r="L5" s="5">
-        <v>419.8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+        <v>2137.9299999999998</v>
+      </c>
+      <c r="I5" s="3">
+        <v>86.002499999999998</v>
+      </c>
+      <c r="J5" s="3">
+        <v>482292.5</v>
+      </c>
+      <c r="K5" s="3">
+        <v>52190</v>
+      </c>
+      <c r="L5" s="3">
+        <v>417.88</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -755,74 +756,74 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>419.8</v>
+        <v>417.88</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="5" cm="1">
+      <c r="H6" s="3" cm="1">
         <f t="array" ref="H6:L6">TRANSPOSE(D9:D13)</f>
-        <v>3178.33</v>
-      </c>
-      <c r="I6" s="5">
-        <v>100.148</v>
-      </c>
-      <c r="J6" s="5">
-        <v>794582.49999999895</v>
-      </c>
-      <c r="K6" s="5">
-        <v>794582.49999999895</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1175.3699999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+        <v>3174.51</v>
+      </c>
+      <c r="I6" s="3">
+        <v>100.053</v>
+      </c>
+      <c r="J6" s="3">
+        <v>713072.5</v>
+      </c>
+      <c r="K6" s="3">
+        <v>80555</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1173.45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="5" cm="1">
+      <c r="H7" s="3" cm="1">
         <f t="array" ref="H7:L7">TRANSPOSE(D16:D20)</f>
-        <v>2946.65</v>
-      </c>
-      <c r="I7" s="5">
-        <v>104.764</v>
-      </c>
-      <c r="J7" s="5">
-        <v>736662.5</v>
-      </c>
-      <c r="K7" s="5">
-        <v>736662.5</v>
-      </c>
-      <c r="L7" s="5">
-        <v>851.37</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+        <v>2942.83</v>
+      </c>
+      <c r="I7" s="3">
+        <v>104.669</v>
+      </c>
+      <c r="J7" s="3">
+        <v>667315</v>
+      </c>
+      <c r="K7" s="3">
+        <v>68392.5</v>
+      </c>
+      <c r="L7" s="3">
+        <v>849.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="5" cm="1">
+      <c r="H8" s="3" cm="1">
         <f t="array" ref="H8:L8">TRANSPOSE(D23:D27)</f>
-        <v>1874.76</v>
-      </c>
-      <c r="I8" s="5">
-        <v>60.463499999999897</v>
-      </c>
-      <c r="J8" s="5">
-        <v>468690</v>
-      </c>
-      <c r="K8" s="5">
-        <v>468690</v>
-      </c>
-      <c r="L8" s="5">
-        <v>665.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+        <v>1870.94</v>
+      </c>
+      <c r="I8" s="3">
+        <v>60.367999999999903</v>
+      </c>
+      <c r="J8" s="3">
+        <v>406320</v>
+      </c>
+      <c r="K8" s="3">
+        <v>61415</v>
+      </c>
+      <c r="L8" s="3">
+        <v>663.58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -830,29 +831,29 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>3178.33</v>
+        <v>3174.51</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="5" cm="1">
+      <c r="H9" s="3" cm="1">
         <f t="array" ref="H9:L9">TRANSPOSE(D30:D34)</f>
-        <v>1707.63</v>
-      </c>
-      <c r="I9" s="5">
-        <v>73.915999999999997</v>
-      </c>
-      <c r="J9" s="5">
-        <v>426907.5</v>
-      </c>
-      <c r="K9" s="5">
-        <v>426907.5</v>
-      </c>
-      <c r="L9" s="5">
-        <v>229.31</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+        <v>1696.95</v>
+      </c>
+      <c r="I9" s="3">
+        <v>73.786000000000001</v>
+      </c>
+      <c r="J9" s="3">
+        <v>424237.5</v>
+      </c>
+      <c r="K9" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="L9" s="3">
+        <v>221.23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -860,10 +861,10 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>100.148</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+        <v>100.053</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>2</v>
       </c>
@@ -871,10 +872,10 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>794582.49999999895</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+        <v>713072.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>3</v>
       </c>
@@ -882,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>794582.49999999895</v>
+        <v>80555</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
@@ -899,7 +900,7 @@
       </c>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>4</v>
       </c>
@@ -907,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>1175.3699999999999</v>
+        <v>1173.45</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
@@ -926,50 +927,50 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="4">
         <v>2143.9</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>86.204999999999998</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="4">
         <v>535975</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="4">
         <v>535975</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="4">
         <v>419.8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="4">
         <v>3178.33</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="4">
         <v>100.148</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
         <v>794582.49999999895</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="4">
         <v>794582.49999999895</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="4">
         <v>1175.3699999999999</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>0</v>
       </c>
@@ -977,28 +978,28 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>2946.65</v>
+        <v>2942.83</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="4">
         <v>2946.65</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="4">
         <v>104.764</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="4">
         <v>736662.5</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="4">
         <v>736662.5</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="4">
         <v>851.37</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>1</v>
       </c>
@@ -1006,28 +1007,28 @@
         <v>5</v>
       </c>
       <c r="D17">
-        <v>104.764</v>
+        <v>104.669</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="4">
         <v>1874.76</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="4">
         <v>60.463499999999897</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="4">
         <v>468690</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="4">
         <v>468690</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="4">
         <v>665.5</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>2</v>
       </c>
@@ -1035,28 +1036,28 @@
         <v>6</v>
       </c>
       <c r="D18">
-        <v>736662.5</v>
+        <v>667315</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="4">
         <v>1707.63</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="4">
         <v>73.915999999999997</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="4">
         <v>426907.5</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="4">
         <v>426907.5</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="4">
         <v>229.31</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>3</v>
       </c>
@@ -1064,10 +1065,10 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>736662.5</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+        <v>68392.5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>4</v>
       </c>
@@ -1075,15 +1076,15 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>851.37</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+        <v>849.45</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>0</v>
       </c>
@@ -1091,10 +1092,10 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>1874.76</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+        <v>1870.94</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>1</v>
       </c>
@@ -1102,10 +1103,10 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>60.463499999999897</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+        <v>60.367999999999903</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>2</v>
       </c>
@@ -1113,10 +1114,10 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>468690</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+        <v>406320</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>3</v>
       </c>
@@ -1124,10 +1125,10 @@
         <v>6</v>
       </c>
       <c r="D26">
-        <v>468690</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+        <v>61415</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>4</v>
       </c>
@@ -1135,15 +1136,15 @@
         <v>5</v>
       </c>
       <c r="D27">
-        <v>665.5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+        <v>663.58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>0</v>
       </c>
@@ -1151,10 +1152,10 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>1707.63</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+        <v>1696.95</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>1</v>
       </c>
@@ -1162,10 +1163,10 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>73.915999999999997</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+        <v>73.786000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>2</v>
       </c>
@@ -1173,21 +1174,22 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>426907.5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+        <f>406257.5+17980</f>
+        <v>424237.5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>3</v>
       </c>
       <c r="C33" t="s">
         <v>6</v>
       </c>
-      <c r="D33">
-        <v>426907.5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>4</v>
       </c>
@@ -1195,7 +1197,7 @@
         <v>5</v>
       </c>
       <c r="D34">
-        <v>229.31</v>
+        <v>221.23</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +1208,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F737E636-C471-4278-8DEE-95918C1B7BF7}">
   <dimension ref="C2:J25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:10" x14ac:dyDescent="0.3">
       <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1222,279 +1224,279 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>22.33</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>53187</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>3000000</v>
       </c>
     </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>-62.302</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>148512</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>5000000</v>
       </c>
     </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>-41.917999999999999</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>99640</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>5000000</v>
       </c>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>-16.98</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>40326</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>2000000</v>
       </c>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>-65.338999999999999</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>155462</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>8000000</v>
       </c>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>-74.614000000000004</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>177722</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>9000000</v>
       </c>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="G10" s="3" t="s">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="G10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
+      <c r="H10" s="9"/>
+      <c r="I10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C11" s="9"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="7"/>
       <c r="G11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H11" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="7">
         <v>2.8929</v>
       </c>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C12" s="9"/>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="7"/>
       <c r="G12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H12" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="7">
         <v>0.45700000000000002</v>
       </c>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C13" s="9"/>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="7"/>
       <c r="G13" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H13" t="s">
         <v>43</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="7">
         <v>0.157</v>
       </c>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C14" s="9"/>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="7"/>
       <c r="G14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H14" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="7">
         <v>0.17100000000000001</v>
       </c>
     </row>
-    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C15" s="9"/>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="7"/>
       <c r="G15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H15" t="s">
         <v>44</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="7">
         <v>2.0899999999999998E-3</v>
       </c>
     </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C16" s="9"/>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="7"/>
       <c r="G16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H16" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="7">
         <v>1.52</v>
       </c>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C17" s="9"/>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="7"/>
       <c r="G17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H17" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="7">
         <v>0.25800000000000001</v>
       </c>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C18" s="9"/>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="7"/>
       <c r="G18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="7">
         <v>1.4500000000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C19" s="9"/>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="7"/>
       <c r="G19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H19" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="7">
         <v>0.46700000000000003</v>
       </c>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="I20" s="9" t="s">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="7">
         <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="10"/>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
